--- a/modelado/modelos/resultados/Regre/BL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/BL_reg.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Climatology_SQA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Climatology_HKP" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -159,6 +160,39 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9344025" cy="3724275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -561,4 +595,127 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5230001776410076</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7312713393400079</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6758220084513091</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.519170257261526</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.798489138410061</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1805879927094023</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.189477404415077</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.2805494306583151</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7884473600160858</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.700027833742039</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L3" t="n">
+        <v>53.88888888888889</v>
+      </c>
+      <c r="M3" t="n">
+        <v>40.06661206661207</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/modelado/modelos/resultados/Regre/BL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/BL_reg.xlsx
@@ -146,7 +146,37 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9458325" cy="3724275"/>
+    <ext cx="9648825" cy="3733800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9534525" cy="3733800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -163,36 +193,6 @@
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9344025" cy="3724275"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/modelado/modelos/resultados/Regre/BL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/BL_reg.xlsx
@@ -160,6 +160,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -190,9 +193,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -552,43 +552,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4168270918360841</v>
+        <v>0.4195538207082934</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6475318614850525</v>
+        <v>0.6552773658208253</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7611535198499323</v>
+        <v>0.740522325088534</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2098342287829601</v>
+        <v>0.206233653666184</v>
       </c>
       <c r="E3" t="n">
-        <v>1.285740413463831</v>
+        <v>1.289161436012599</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09873242701663709</v>
+        <v>0.09899512845744236</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7291023115459575</v>
+        <v>0.7213532147783708</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.07553624910754828</v>
+        <v>-0.1629565972964673</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4090236150922318</v>
+        <v>0.4323243479393053</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5747659045064557</v>
+        <v>0.5831526697586564</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.6422222222222222</v>
       </c>
       <c r="L3" t="n">
-        <v>64.44444444444444</v>
+        <v>64.22222222222223</v>
       </c>
       <c r="M3" t="n">
-        <v>46.40884688203649</v>
+        <v>40.96168239721094</v>
       </c>
     </row>
   </sheetData>
@@ -675,43 +675,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5230001776410076</v>
+        <v>0.4840947845575136</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7312713393400079</v>
+        <v>0.7271653147301211</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6758220084513091</v>
+        <v>0.503665771472553</v>
       </c>
       <c r="D3" t="n">
-        <v>0.519170257261526</v>
+        <v>0.4847741041756881</v>
       </c>
       <c r="E3" t="n">
-        <v>1.798489138410061</v>
+        <v>1.875002869619854</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1805879927094023</v>
+        <v>0.1598734802400227</v>
       </c>
       <c r="G3" t="n">
-        <v>1.189477404415077</v>
+        <v>1.265994331535862</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2805494306583151</v>
+        <v>-0.5148475315819079</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7884473600160858</v>
+        <v>0.9418237187244263</v>
       </c>
       <c r="J3" t="n">
-        <v>0.700027833742039</v>
+        <v>0.6992591694589725</v>
       </c>
       <c r="K3" t="n">
-        <v>0.54</v>
+        <v>0.5211111111111111</v>
       </c>
       <c r="L3" t="n">
-        <v>53.88888888888889</v>
+        <v>51.55555555555556</v>
       </c>
       <c r="M3" t="n">
-        <v>40.06661206661207</v>
+        <v>38.51105651105652</v>
       </c>
     </row>
   </sheetData>

--- a/modelado/modelos/resultados/Regre/BL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/BL_reg.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Climatology_SQA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Climatology_HKP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Climatology_HKP_VALIDATION" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -171,6 +172,39 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9534525" cy="3733800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -552,43 +586,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4195538207082934</v>
+        <v>0.4430026205717584</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6552773658208253</v>
+        <v>0.6852439642870658</v>
       </c>
       <c r="C3" t="n">
-        <v>0.740522325088534</v>
+        <v>0.7479639319454111</v>
       </c>
       <c r="D3" t="n">
-        <v>0.206233653666184</v>
+        <v>0.2359691973378547</v>
       </c>
       <c r="E3" t="n">
-        <v>1.289161436012599</v>
+        <v>1.322820305163927</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09899512845744236</v>
+        <v>0.1150355995264263</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7213532147783708</v>
+        <v>0.7232032813715208</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1629565972964673</v>
+        <v>-0.2335576541592657</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4323243479393053</v>
+        <v>0.4745880368884845</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5831526697586564</v>
+        <v>0.6119041954193301</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6422222222222222</v>
+        <v>0.6866666666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>64.22222222222223</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>40.96168239721094</v>
+        <v>44.95940094849977</v>
       </c>
     </row>
   </sheetData>
@@ -675,43 +709,166 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4840947845575136</v>
+        <v>0.4645123329568612</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7271653147301211</v>
+        <v>0.740993667463432</v>
       </c>
       <c r="C3" t="n">
-        <v>0.503665771472553</v>
+        <v>0.2898343558775026</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4847741041756881</v>
+        <v>0.4737718392814795</v>
       </c>
       <c r="E3" t="n">
-        <v>1.875002869619854</v>
+        <v>2.005894997351408</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1598734802400227</v>
+        <v>0.2051810744104688</v>
       </c>
       <c r="G3" t="n">
-        <v>1.265994331535862</v>
+        <v>1.367668735647781</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5148475315819079</v>
+        <v>-0.7254168345248239</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9418237187244263</v>
+        <v>1.111134735192364</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6992591694589725</v>
+        <v>0.7086836697556351</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5211111111111111</v>
+        <v>0.4533333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>51.55555555555556</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>38.51105651105652</v>
+        <v>34.01801801801802</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.4900652793186657</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7201882877401492</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6145980894234191</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4866265518558919</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.810999985376408</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1544162278724711</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.218731856835913</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.410119930924127</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8569799049934079</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6926564534670099</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5433333333333333</v>
+      </c>
+      <c r="L3" t="n">
+        <v>55</v>
+      </c>
+      <c r="M3" t="n">
+        <v>40.59090909090909</v>
       </c>
     </row>
   </sheetData>

--- a/modelado/modelos/resultados/Regre/BL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/BL_reg.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Climatology_SQA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Climatology_HKP" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Climatology_HKP_VALIDATION" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Climatology_SQA_VALIDATION" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -214,6 +215,39 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="9534525" cy="3733800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9648825" cy="3733800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -586,43 +620,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4430026205717584</v>
+        <v>0.4520920988270544</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6852439642870658</v>
+        <v>0.6889831986599464</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7479639319454111</v>
+        <v>0.7576182829221412</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2359691973378547</v>
+        <v>0.2365826787255935</v>
       </c>
       <c r="E3" t="n">
-        <v>1.322820305163927</v>
+        <v>1.311982548811041</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1150355995264263</v>
+        <v>0.1140931224607896</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7232032813715208</v>
+        <v>0.716575580250613</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2335576541592657</v>
+        <v>-0.2174178842714514</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4745880368884845</v>
+        <v>0.4609373136992828</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6119041954193301</v>
+        <v>0.6170925061297686</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.6766666666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>68.66666666666667</v>
+        <v>67.66666666666666</v>
       </c>
       <c r="M3" t="n">
-        <v>44.95940094849977</v>
+        <v>46.0796696605868</v>
       </c>
     </row>
   </sheetData>
@@ -875,4 +909,127 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.391784400495798</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6315869045381513</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7307647072380077</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1871540692081242</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.286653063217404</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1005332971399811</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7284348261225326</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.1369070019453636</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.422169692039703</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5646544508517005</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L3" t="n">
+        <v>62</v>
+      </c>
+      <c r="M3" t="n">
+        <v>37.90268876552302</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/modelado/modelos/resultados/Regre/BL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/BL_reg.xlsx
@@ -137,135 +137,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9648825" cy="3733800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9534525" cy="3733800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9534525" cy="3733800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9648825" cy="3733800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -661,7 +532,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -784,7 +654,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -907,7 +776,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1030,6 +898,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/modelado/modelos/resultados/Regre/BL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/BL_reg.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M3"/>
+  <dimension ref="A2:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -435,99 +435,59 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>r2_plot</t>
+          <t>rmse</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>mean_ssim</t>
+          <t>nrmse</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>rmse</t>
+          <t>mae</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>nrmse</t>
+          <t>mbe</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>mae</t>
+          <t>w_dist</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>mbe</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>w_dist</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
           <t>spearman_corr</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>hit_rate_percent</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>mean_yearly_hit_rate</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>mean_monthly_hit_rate</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4520920988270544</v>
+        <v>0.4711147727940651</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6889831986599464</v>
+        <v>0.69272191719451</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7576182829221412</v>
+        <v>1.289006166445736</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2365826787255935</v>
+        <v>0.1120950416103344</v>
       </c>
       <c r="E3" t="n">
-        <v>1.311982548811041</v>
+        <v>0.7105488935043356</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1140931224607896</v>
+        <v>-0.128485137168366</v>
       </c>
       <c r="G3" t="n">
-        <v>0.716575580250613</v>
+        <v>0.4374930193405363</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2174178842714514</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.4609373136992828</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6170925061297686</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.6766666666666666</v>
-      </c>
-      <c r="L3" t="n">
-        <v>67.66666666666666</v>
-      </c>
-      <c r="M3" t="n">
-        <v>46.0796696605868</v>
+        <v>0.6462244645273413</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M3"/>
+  <dimension ref="A2:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -557,99 +517,67 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>r2_plot</t>
+          <t>mean_ssim</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>mean_ssim</t>
+          <t>rmse</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>rmse</t>
+          <t>nrmse</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>nrmse</t>
+          <t>mae</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>mae</t>
+          <t>mbe</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>mbe</t>
+          <t>w_dist</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>w_dist</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
           <t>spearman_corr</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>hit_rate_percent</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>mean_yearly_hit_rate</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>mean_monthly_hit_rate</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4645123329568612</v>
+        <v>0.4959605888343597</v>
       </c>
       <c r="B3" t="n">
-        <v>0.740993667463432</v>
+        <v>0.7567749718458761</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2898343558775026</v>
+        <v>0.4934155266688534</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4737718392814795</v>
+        <v>1.946102482084008</v>
       </c>
       <c r="E3" t="n">
-        <v>2.005894997351408</v>
+        <v>0.1990649554010148</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2051810744104688</v>
+        <v>1.329999756063819</v>
       </c>
       <c r="G3" t="n">
-        <v>1.367668735647781</v>
+        <v>-0.674151843159308</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7254168345248239</v>
+        <v>1.086185169777135</v>
       </c>
       <c r="I3" t="n">
-        <v>1.111134735192364</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.7086836697556351</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.4533333333333333</v>
-      </c>
-      <c r="L3" t="n">
-        <v>45.33333333333333</v>
-      </c>
-      <c r="M3" t="n">
-        <v>34.01801801801802</v>
+        <v>0.7233292754183939</v>
       </c>
     </row>
   </sheetData>

--- a/modelado/modelos/resultados/Regre/BL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/BL_reg.xlsx
@@ -466,28 +466,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4711147727940651</v>
+        <v>0.4641626066930653</v>
       </c>
       <c r="B3" t="n">
-        <v>0.69272191719451</v>
+        <v>0.6873131035287916</v>
       </c>
       <c r="C3" t="n">
-        <v>1.289006166445736</v>
+        <v>1.29745046330825</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1120950416103344</v>
+        <v>0.1128293777468198</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7105488935043356</v>
+        <v>0.7143583769981272</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.128485137168366</v>
+        <v>-0.1294427879064783</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4374930193405363</v>
+        <v>0.4322465394058408</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6462244645273413</v>
+        <v>0.6317708023931353</v>
       </c>
     </row>
   </sheetData>
